--- a/Lisa Project/Lisa's project.xlsx
+++ b/Lisa Project/Lisa's project.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\C語言\C-Learning\Lisa Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD4E1962-E159-4018-9EFF-6E3169B76A82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31346986-2FA4-4359-BCEA-87A8DEAA6256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{DA1E983E-EF55-4F84-98AC-5E562C614A6E}"/>
   </bookViews>
@@ -232,7 +232,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -259,6 +259,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2722,10 +2728,18 @@
         <v>1</v>
       </c>
       <c r="C92">
+        <v>0</v>
+      </c>
+      <c r="D92">
         <v>1</v>
       </c>
-      <c r="D92">
-        <v>2</v>
+      <c r="F92" s="9">
+        <f>(B92/3)</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="G92" s="10">
+        <f>ROUNDDOWN(F92,0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.3">
@@ -2733,10 +2747,18 @@
         <v>2</v>
       </c>
       <c r="C93">
+        <v>0</v>
+      </c>
+      <c r="D93">
         <v>1</v>
       </c>
-      <c r="D93">
-        <v>2</v>
+      <c r="F93" s="9">
+        <f t="shared" ref="F93:F115" si="0">(B93/3)</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="G93" s="10">
+        <f t="shared" ref="G93:G115" si="1">ROUNDDOWN(F93,0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.3">
@@ -2744,10 +2766,18 @@
         <v>3</v>
       </c>
       <c r="C94">
+        <v>0</v>
+      </c>
+      <c r="D94">
         <v>1</v>
       </c>
-      <c r="D94">
-        <v>2</v>
+      <c r="F94" s="9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G94" s="10">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="2:11" x14ac:dyDescent="0.3">
@@ -2755,10 +2785,18 @@
         <v>4</v>
       </c>
       <c r="C95">
+        <v>2</v>
+      </c>
+      <c r="D95">
         <v>3</v>
       </c>
-      <c r="D95">
-        <v>4</v>
+      <c r="F95" s="9">
+        <f t="shared" si="0"/>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="G95" s="10">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
     </row>
     <row r="96" spans="2:11" x14ac:dyDescent="0.3">
@@ -2766,219 +2804,379 @@
         <v>5</v>
       </c>
       <c r="C96">
+        <v>2</v>
+      </c>
+      <c r="D96">
         <v>3</v>
       </c>
-      <c r="D96">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="F96" s="9">
+        <f t="shared" si="0"/>
+        <v>1.6666666666666667</v>
+      </c>
+      <c r="G96" s="10">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B97">
         <v>6</v>
       </c>
       <c r="C97">
+        <v>2</v>
+      </c>
+      <c r="D97">
         <v>3</v>
       </c>
-      <c r="D97">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="98" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="F97" s="9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G97" s="10">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B98">
         <v>7</v>
       </c>
       <c r="C98">
+        <v>0</v>
+      </c>
+      <c r="D98">
         <v>1</v>
       </c>
-      <c r="D98">
+      <c r="F98" s="9">
+        <f t="shared" si="0"/>
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="G98" s="10">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B99">
         <v>8</v>
       </c>
       <c r="C99">
+        <v>0</v>
+      </c>
+      <c r="D99">
         <v>1</v>
       </c>
-      <c r="D99">
+      <c r="F99" s="9">
+        <f t="shared" si="0"/>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="G99" s="10">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B100">
         <v>9</v>
       </c>
       <c r="C100">
+        <v>0</v>
+      </c>
+      <c r="D100">
         <v>1</v>
       </c>
-      <c r="D100">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="101" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="F100" s="9">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G100" s="10">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B101">
         <v>10</v>
       </c>
       <c r="C101">
+        <v>2</v>
+      </c>
+      <c r="D101">
         <v>3</v>
       </c>
-      <c r="D101">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="102" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="F101" s="9">
+        <f t="shared" si="0"/>
+        <v>3.3333333333333335</v>
+      </c>
+      <c r="G101" s="10">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B102">
         <v>11</v>
       </c>
       <c r="C102">
+        <v>2</v>
+      </c>
+      <c r="D102">
         <v>3</v>
       </c>
-      <c r="D102">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="103" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="F102" s="9">
+        <f t="shared" si="0"/>
+        <v>3.6666666666666665</v>
+      </c>
+      <c r="G102" s="10">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="103" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B103">
         <v>12</v>
       </c>
       <c r="C103">
+        <v>2</v>
+      </c>
+      <c r="D103">
         <v>3</v>
       </c>
-      <c r="D103">
+      <c r="F103" s="9">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
-    </row>
-    <row r="104" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="G103" s="10">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B104">
         <v>13</v>
       </c>
       <c r="C104">
+        <v>0</v>
+      </c>
+      <c r="D104">
         <v>1</v>
       </c>
-      <c r="D104">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="105" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="F104" s="9">
+        <f t="shared" si="0"/>
+        <v>4.333333333333333</v>
+      </c>
+      <c r="G104" s="10">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B105">
         <v>14</v>
       </c>
       <c r="C105">
+        <v>0</v>
+      </c>
+      <c r="D105">
         <v>1</v>
       </c>
-      <c r="D105">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="106" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="F105" s="9">
+        <f t="shared" si="0"/>
+        <v>4.666666666666667</v>
+      </c>
+      <c r="G105" s="10">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B106">
         <v>15</v>
       </c>
       <c r="C106">
+        <v>0</v>
+      </c>
+      <c r="D106">
         <v>1</v>
       </c>
-      <c r="D106">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="107" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="F106" s="9">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="G106" s="10">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="107" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B107">
         <v>16</v>
       </c>
       <c r="C107">
+        <v>2</v>
+      </c>
+      <c r="D107">
         <v>3</v>
       </c>
-      <c r="D107">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="108" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="F107" s="9">
+        <f t="shared" si="0"/>
+        <v>5.333333333333333</v>
+      </c>
+      <c r="G107" s="10">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B108">
         <v>17</v>
       </c>
       <c r="C108">
+        <v>2</v>
+      </c>
+      <c r="D108">
         <v>3</v>
       </c>
-      <c r="D108">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="109" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="F108" s="9">
+        <f t="shared" si="0"/>
+        <v>5.666666666666667</v>
+      </c>
+      <c r="G108" s="10">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B109">
         <v>18</v>
       </c>
       <c r="C109">
+        <v>2</v>
+      </c>
+      <c r="D109">
         <v>3</v>
       </c>
-      <c r="D109">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="110" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="F109" s="9">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="G109" s="10">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="110" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B110">
         <v>19</v>
       </c>
       <c r="C110">
+        <v>0</v>
+      </c>
+      <c r="D110">
         <v>1</v>
       </c>
-      <c r="D110">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="111" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="F110" s="9">
+        <f t="shared" si="0"/>
+        <v>6.333333333333333</v>
+      </c>
+      <c r="G110" s="10">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="111" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B111">
         <v>20</v>
       </c>
       <c r="C111">
+        <v>0</v>
+      </c>
+      <c r="D111">
         <v>1</v>
       </c>
-      <c r="D111">
+      <c r="F111" s="9">
+        <f t="shared" si="0"/>
+        <v>6.666666666666667</v>
+      </c>
+      <c r="G111" s="10">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="112" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B112">
+        <v>21</v>
+      </c>
+      <c r="C112">
+        <v>0</v>
+      </c>
+      <c r="D112">
+        <v>1</v>
+      </c>
+      <c r="F112" s="9">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="G112" s="10">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="113" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B113">
+        <v>22</v>
+      </c>
+      <c r="C113">
         <v>2</v>
       </c>
-    </row>
-    <row r="112" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B112">
-        <v>21</v>
-      </c>
-      <c r="C112">
-        <v>1</v>
-      </c>
-      <c r="D112">
+      <c r="D113">
+        <v>3</v>
+      </c>
+      <c r="F113" s="9">
+        <f t="shared" si="0"/>
+        <v>7.333333333333333</v>
+      </c>
+      <c r="G113" s="10">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="114" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B114">
+        <v>23</v>
+      </c>
+      <c r="C114">
         <v>2</v>
       </c>
-    </row>
-    <row r="113" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B113">
-        <v>22</v>
-      </c>
-      <c r="C113">
+      <c r="D114">
         <v>3</v>
       </c>
-      <c r="D113">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="114" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B114">
-        <v>23</v>
-      </c>
-      <c r="C114">
-        <v>3</v>
-      </c>
-      <c r="D114">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="115" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="F114" s="9">
+        <f t="shared" si="0"/>
+        <v>7.666666666666667</v>
+      </c>
+      <c r="G114" s="10">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="115" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B115">
         <v>24</v>
       </c>
       <c r="C115">
+        <v>2</v>
+      </c>
+      <c r="D115">
         <v>3</v>
       </c>
-      <c r="D115">
-        <v>4</v>
+      <c r="F115" s="9">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="G115" s="10">
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/Lisa Project/Lisa's project.xlsx
+++ b/Lisa Project/Lisa's project.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\C語言\C-Learning\Lisa Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{043BA1A1-3522-421C-B3FE-0BAF206B30D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{388D3B8E-AE8E-4E1D-8B0C-F99F5F4D7238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DA1E983E-EF55-4F84-98AC-5E562C614A6E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{DA1E983E-EF55-4F84-98AC-5E562C614A6E}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
+    <sheet name="工作表2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="60">
   <si>
     <t>A</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -161,6 +162,93 @@
   <si>
     <t>B(事假)</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>week</t>
+  </si>
+  <si>
+    <t>Day</t>
+  </si>
+  <si>
+    <t>Evening</t>
+  </si>
+  <si>
+    <t>Night</t>
+  </si>
+  <si>
+    <t>DM</t>
+  </si>
+  <si>
+    <t>Brine</t>
+  </si>
+  <si>
+    <t>HCl</t>
+  </si>
+  <si>
+    <t>Sat</t>
+  </si>
+  <si>
+    <t>Carol</t>
+  </si>
+  <si>
+    <t>Frank</t>
+  </si>
+  <si>
+    <t>Iris</t>
+  </si>
+  <si>
+    <t>Louis</t>
+  </si>
+  <si>
+    <t>Sun</t>
+  </si>
+  <si>
+    <t>Mon</t>
+  </si>
+  <si>
+    <t>Tue</t>
+  </si>
+  <si>
+    <t>Wed</t>
+  </si>
+  <si>
+    <t>Thu</t>
+  </si>
+  <si>
+    <t>Fri</t>
+  </si>
+  <si>
+    <t>Day-off</t>
+  </si>
+  <si>
+    <t>Leave</t>
+  </si>
+  <si>
+    <t>Alice0</t>
+  </si>
+  <si>
+    <t>David1</t>
+  </si>
+  <si>
+    <t>Grog2</t>
+  </si>
+  <si>
+    <t>Jackson3</t>
+  </si>
+  <si>
+    <t>Bruce0</t>
+  </si>
+  <si>
+    <t>Eason2</t>
+  </si>
+  <si>
+    <t>Hank4</t>
+  </si>
+  <si>
+    <t>Ken6</t>
   </si>
 </sst>
 </file>
@@ -200,12 +288,47 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -214,7 +337,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -254,12 +377,217 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="25">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor auto="1"/>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF339966"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCCCFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCC99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCC9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF9999FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFAE0F5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor auto="1"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF339966"/>
+      <color rgb="FFCCCCFF"/>
+      <color rgb="FFCCFF33"/>
+      <color rgb="FFFFCC99"/>
+      <color rgb="FFCC9900"/>
+      <color rgb="FFCCFFFF"/>
+      <color rgb="FF9999FF"/>
+      <color rgb="FFFAE0F5"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -569,56 +897,56 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{201778D1-075F-4051-8320-17672C409E34}">
   <dimension ref="C5:AA61"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.08203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.4140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.4140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.4140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.4140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.75" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="9" customWidth="1"/>
-    <col min="15" max="15" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.4140625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="18.6640625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.109375" customWidth="1"/>
-    <col min="22" max="22" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.08203125" customWidth="1"/>
+    <col min="22" max="22" width="15.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="4:27" x14ac:dyDescent="0.25">
-      <c r="D5" s="4" t="s">
+    <row r="5" spans="4:27" x14ac:dyDescent="0.3">
+      <c r="D5" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4" t="s">
+      <c r="E5" s="13"/>
+      <c r="F5" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4" t="s">
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4" t="s">
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4" t="s">
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="4"/>
-      <c r="R5" s="4" t="s">
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="S5" s="4"/>
-      <c r="T5" s="4"/>
-    </row>
-    <row r="6" spans="4:27" x14ac:dyDescent="0.25">
+      <c r="S5" s="13"/>
+      <c r="T5" s="13"/>
+    </row>
+    <row r="6" spans="4:27" x14ac:dyDescent="0.3">
       <c r="F6" s="1" t="s">
         <v>12</v>
       </c>
@@ -668,7 +996,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="4:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="4:27" x14ac:dyDescent="0.3">
       <c r="D7" s="2">
         <v>46235</v>
       </c>
@@ -718,7 +1046,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="4:27" x14ac:dyDescent="0.25">
+    <row r="8" spans="4:27" x14ac:dyDescent="0.3">
       <c r="D8" s="2">
         <v>46236</v>
       </c>
@@ -765,7 +1093,7 @@
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
     </row>
-    <row r="9" spans="4:27" x14ac:dyDescent="0.25">
+    <row r="9" spans="4:27" x14ac:dyDescent="0.3">
       <c r="D9" s="2">
         <v>46237</v>
       </c>
@@ -812,7 +1140,7 @@
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
     </row>
-    <row r="10" spans="4:27" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="4:27" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D10" s="9">
         <v>46238</v>
       </c>
@@ -859,7 +1187,7 @@
       <c r="S10" s="11"/>
       <c r="T10" s="11"/>
     </row>
-    <row r="11" spans="4:27" x14ac:dyDescent="0.25">
+    <row r="11" spans="4:27" x14ac:dyDescent="0.3">
       <c r="D11" s="2">
         <v>46239</v>
       </c>
@@ -906,7 +1234,7 @@
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
     </row>
-    <row r="12" spans="4:27" x14ac:dyDescent="0.25">
+    <row r="12" spans="4:27" x14ac:dyDescent="0.3">
       <c r="D12" s="2">
         <v>46240</v>
       </c>
@@ -953,7 +1281,7 @@
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
     </row>
-    <row r="13" spans="4:27" x14ac:dyDescent="0.25">
+    <row r="13" spans="4:27" x14ac:dyDescent="0.3">
       <c r="D13" s="2">
         <v>46241</v>
       </c>
@@ -1000,7 +1328,7 @@
       <c r="S13" s="1"/>
       <c r="T13" s="1"/>
     </row>
-    <row r="14" spans="4:27" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="4:27" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D14" s="5">
         <v>46242</v>
       </c>
@@ -1047,7 +1375,7 @@
       <c r="S14" s="7"/>
       <c r="T14" s="7"/>
     </row>
-    <row r="15" spans="4:27" x14ac:dyDescent="0.25">
+    <row r="15" spans="4:27" x14ac:dyDescent="0.3">
       <c r="D15" s="2">
         <v>46243</v>
       </c>
@@ -1094,7 +1422,7 @@
       <c r="Z15" s="1"/>
       <c r="AA15" s="1"/>
     </row>
-    <row r="16" spans="4:27" x14ac:dyDescent="0.25">
+    <row r="16" spans="4:27" x14ac:dyDescent="0.3">
       <c r="D16" s="2">
         <v>46244</v>
       </c>
@@ -1141,7 +1469,7 @@
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
     </row>
-    <row r="17" spans="4:20" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D17" s="5">
         <v>46245</v>
       </c>
@@ -1188,7 +1516,7 @@
       <c r="S17" s="7"/>
       <c r="T17" s="7"/>
     </row>
-    <row r="18" spans="4:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D18" s="2">
         <v>46246</v>
       </c>
@@ -1235,7 +1563,7 @@
       <c r="S18" s="1"/>
       <c r="T18" s="1"/>
     </row>
-    <row r="19" spans="4:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D19" s="2">
         <v>46247</v>
       </c>
@@ -1282,7 +1610,7 @@
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
     </row>
-    <row r="20" spans="4:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D20" s="2">
         <v>46248</v>
       </c>
@@ -1329,7 +1657,7 @@
       <c r="S20" s="1"/>
       <c r="T20" s="1"/>
     </row>
-    <row r="21" spans="4:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D21" s="2">
         <v>46249</v>
       </c>
@@ -1376,7 +1704,7 @@
       <c r="S21" s="1"/>
       <c r="T21" s="1"/>
     </row>
-    <row r="22" spans="4:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D22" s="2">
         <v>46250</v>
       </c>
@@ -1423,7 +1751,7 @@
       <c r="S22" s="1"/>
       <c r="T22" s="1"/>
     </row>
-    <row r="23" spans="4:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D23" s="2">
         <v>46251</v>
       </c>
@@ -1470,7 +1798,7 @@
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
     </row>
-    <row r="24" spans="4:20" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="4:20" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D24" s="5">
         <v>46252</v>
       </c>
@@ -1519,7 +1847,7 @@
       </c>
       <c r="T24" s="7"/>
     </row>
-    <row r="25" spans="4:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D25" s="2">
         <v>46253</v>
       </c>
@@ -1566,7 +1894,7 @@
       <c r="S25" s="1"/>
       <c r="T25" s="1"/>
     </row>
-    <row r="26" spans="4:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D26" s="2">
         <v>46254</v>
       </c>
@@ -1613,7 +1941,7 @@
       <c r="S26" s="1"/>
       <c r="T26" s="1"/>
     </row>
-    <row r="27" spans="4:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D27" s="2">
         <v>46255</v>
       </c>
@@ -1660,7 +1988,7 @@
       <c r="S27" s="1"/>
       <c r="T27" s="1"/>
     </row>
-    <row r="28" spans="4:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D28" s="2">
         <v>46256</v>
       </c>
@@ -1707,7 +2035,7 @@
       <c r="S28" s="1"/>
       <c r="T28" s="1"/>
     </row>
-    <row r="29" spans="4:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D29" s="2">
         <v>46257</v>
       </c>
@@ -1754,7 +2082,7 @@
       <c r="S29" s="1"/>
       <c r="T29" s="1"/>
     </row>
-    <row r="30" spans="4:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D30" s="2">
         <v>46258</v>
       </c>
@@ -1801,7 +2129,7 @@
       <c r="S30" s="1"/>
       <c r="T30" s="1"/>
     </row>
-    <row r="31" spans="4:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D31" s="2">
         <v>46259</v>
       </c>
@@ -1848,7 +2176,7 @@
       <c r="S31" s="1"/>
       <c r="T31" s="1"/>
     </row>
-    <row r="32" spans="4:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D32" s="2">
         <v>46260</v>
       </c>
@@ -1895,7 +2223,7 @@
       <c r="S32" s="1"/>
       <c r="T32" s="1"/>
     </row>
-    <row r="33" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:20" x14ac:dyDescent="0.3">
       <c r="D33" s="2">
         <v>46261</v>
       </c>
@@ -1942,7 +2270,7 @@
       <c r="S33" s="1"/>
       <c r="T33" s="1"/>
     </row>
-    <row r="34" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:20" x14ac:dyDescent="0.3">
       <c r="D34" s="2">
         <v>46262</v>
       </c>
@@ -1989,7 +2317,7 @@
       <c r="S34" s="1"/>
       <c r="T34" s="1"/>
     </row>
-    <row r="35" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:20" x14ac:dyDescent="0.3">
       <c r="D35" s="2">
         <v>46263</v>
       </c>
@@ -2036,7 +2364,7 @@
       <c r="S35" s="1"/>
       <c r="T35" s="1"/>
     </row>
-    <row r="36" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:20" x14ac:dyDescent="0.3">
       <c r="D36" s="2">
         <v>46264</v>
       </c>
@@ -2083,7 +2411,7 @@
       <c r="S36" s="1"/>
       <c r="T36" s="1"/>
     </row>
-    <row r="37" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:20" x14ac:dyDescent="0.3">
       <c r="D37" s="2">
         <v>46265</v>
       </c>
@@ -2130,7 +2458,7 @@
       <c r="S37" s="1"/>
       <c r="T37" s="1"/>
     </row>
-    <row r="43" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:20" x14ac:dyDescent="0.3">
       <c r="I43">
         <v>1</v>
       </c>
@@ -2150,7 +2478,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C44">
         <v>0</v>
       </c>
@@ -2184,7 +2512,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C45">
         <f>MOD((C44+1),4)</f>
         <v>1</v>
@@ -2226,7 +2554,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C46">
         <f>MOD((C44+2),4)</f>
         <v>2</v>
@@ -2244,7 +2572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C47">
         <f>MOD((C44+3),4)</f>
         <v>3</v>
@@ -2265,7 +2593,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:20" x14ac:dyDescent="0.3">
       <c r="I48">
         <v>3</v>
       </c>
@@ -2277,7 +2605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C49">
         <v>1</v>
       </c>
@@ -2301,7 +2629,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C50">
         <v>2</v>
       </c>
@@ -2315,7 +2643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C51">
         <v>3</v>
       </c>
@@ -2329,7 +2657,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C53">
         <v>0</v>
       </c>
@@ -2343,7 +2671,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C54">
         <f>MOD(C53+2,7)</f>
         <v>2</v>
@@ -2361,7 +2689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C55">
         <f>MOD(C53+4,7)</f>
         <v>4</v>
@@ -2379,7 +2707,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C56">
         <f>MOD(C53+6,7)</f>
         <v>6</v>
@@ -2397,7 +2725,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C59">
         <v>2</v>
       </c>
@@ -2411,7 +2739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C60">
         <v>4</v>
       </c>
@@ -2425,7 +2753,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C61">
         <v>6</v>
       </c>
@@ -2452,4 +2780,1703 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC5B9C8A-20B7-4BD8-AC90-189B0DB1623A}">
+  <dimension ref="B2:R44"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="14" width="8.6640625" style="4"/>
+    <col min="15" max="15" width="7.1640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.6640625" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:18" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="2:18" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="K3" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="L3" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="M3" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="N3" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="O3" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="P3" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q3" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="R3" s="15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B4" s="2">
+        <v>46235</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B5" s="2">
+        <v>46236</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B6" s="2">
+        <v>46237</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B7" s="2">
+        <v>46238</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B8" s="2">
+        <v>46239</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B9" s="2">
+        <v>46240</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B10" s="2">
+        <v>46241</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="N10" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="O10" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B11" s="2">
+        <v>46242</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="N11" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="O11" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B12" s="2">
+        <v>46243</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="N12" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="O12" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B13" s="2">
+        <v>46244</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="N13" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="O13" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B14" s="2">
+        <v>46245</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="N14" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="O14" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B15" s="2">
+        <v>46246</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="N15" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="O15" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B16" s="2">
+        <v>46247</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="N16" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="O16" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B17" s="2">
+        <v>46248</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="N17" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="O17" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B18" s="2">
+        <v>46249</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="N18" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="O18" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B19" s="2">
+        <v>46250</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="L19" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="M19" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="N19" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="O19" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B20" s="2">
+        <v>46251</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="L20" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="N20" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="O20" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B21" s="2">
+        <v>46252</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="L21" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="N21" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="O21" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B22" s="2">
+        <v>46253</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="L22" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="N22" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="O22" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B23" s="2">
+        <v>46254</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="L23" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="N23" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="O23" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B24" s="2">
+        <v>46255</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="L24" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M24" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="N24" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="O24" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B25" s="2">
+        <v>46256</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="L25" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="N25" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="O25" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B26" s="2">
+        <v>46257</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="L26" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M26" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="N26" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="O26" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="2:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B27" s="17">
+        <v>46258</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F27" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G27" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="H27" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="I27" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="J27" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="K27" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="L27" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="M27" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="N27" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="O27" s="14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B28" s="2">
+        <v>46259</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="L28" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M28" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="N28" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="O28" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B29" s="2">
+        <v>46260</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K29" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="L29" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M29" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="N29" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="O29" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B30" s="2">
+        <v>46261</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="L30" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="M30" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="N30" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="O30" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B31" s="2">
+        <v>46262</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="L31" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="M31" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="N31" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="O31" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B32" s="2">
+        <v>46263</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="L32" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="M32" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="N32" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="O32" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B33" s="17">
+        <v>46264</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="F33" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="G33" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="H33" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="I33" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="J33" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="K33" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="L33" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="M33" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="N33" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="O33" s="14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B34" s="2">
+        <v>46265</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="L34" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="M34" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="N34" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="O34" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="C39" s="16">
+        <v>1</v>
+      </c>
+      <c r="D39" s="16">
+        <v>0</v>
+      </c>
+      <c r="E39" s="16">
+        <v>1</v>
+      </c>
+      <c r="F39" s="16">
+        <v>2</v>
+      </c>
+      <c r="G39" s="16">
+        <v>3</v>
+      </c>
+      <c r="H39" s="4">
+        <f>QUOTIENT(C39,5)+1</f>
+        <v>1</v>
+      </c>
+      <c r="I39" s="4">
+        <f>MOD(D39 + H39,4)</f>
+        <v>1</v>
+      </c>
+      <c r="J39" s="4">
+        <f>QUOTIENT(C39,3)+2</f>
+        <v>2</v>
+      </c>
+      <c r="K39" s="4">
+        <f>MOD(E39 + J39,4)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="C40" s="16">
+        <v>2</v>
+      </c>
+      <c r="D40" s="16">
+        <v>0</v>
+      </c>
+      <c r="E40" s="16">
+        <v>1</v>
+      </c>
+      <c r="F40" s="16">
+        <v>2</v>
+      </c>
+      <c r="G40" s="16">
+        <v>3</v>
+      </c>
+      <c r="H40" s="4">
+        <f t="shared" ref="H40:H44" si="0">QUOTIENT(C40,5)+1</f>
+        <v>1</v>
+      </c>
+      <c r="I40" s="4">
+        <f t="shared" ref="I40:I44" si="1">MOD(D40 + H40,4)</f>
+        <v>1</v>
+      </c>
+      <c r="J40" s="4">
+        <f t="shared" ref="J40:J44" si="2">QUOTIENT(C40,3)+2</f>
+        <v>2</v>
+      </c>
+      <c r="K40" s="4">
+        <f t="shared" ref="K40:K44" si="3">MOD(E40 + J40,4)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="C41" s="16">
+        <v>3</v>
+      </c>
+      <c r="D41" s="16">
+        <v>0</v>
+      </c>
+      <c r="E41" s="16">
+        <v>1</v>
+      </c>
+      <c r="F41" s="16">
+        <v>3</v>
+      </c>
+      <c r="G41" s="16">
+        <v>2</v>
+      </c>
+      <c r="H41" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I41" s="4">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="J41" s="4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="K41" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="C42" s="16">
+        <v>4</v>
+      </c>
+      <c r="D42" s="16">
+        <v>0</v>
+      </c>
+      <c r="E42" s="16">
+        <v>1</v>
+      </c>
+      <c r="F42" s="16">
+        <v>3</v>
+      </c>
+      <c r="G42" s="16">
+        <v>2</v>
+      </c>
+      <c r="H42" s="4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I42" s="4">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="J42" s="4">
+        <f>QUOTIENT(C42,3)+2</f>
+        <v>3</v>
+      </c>
+      <c r="K42" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="C43" s="16">
+        <v>5</v>
+      </c>
+      <c r="D43" s="16">
+        <v>0</v>
+      </c>
+      <c r="E43" s="16">
+        <v>2</v>
+      </c>
+      <c r="F43" s="16">
+        <v>3</v>
+      </c>
+      <c r="G43" s="16">
+        <v>1</v>
+      </c>
+      <c r="H43" s="4">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="I43" s="4">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="J43" s="4">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="K43" s="4">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="C44" s="16">
+        <v>6</v>
+      </c>
+      <c r="D44" s="16">
+        <v>0</v>
+      </c>
+      <c r="E44" s="16">
+        <v>2</v>
+      </c>
+      <c r="F44" s="16">
+        <v>3</v>
+      </c>
+      <c r="G44" s="16">
+        <v>1</v>
+      </c>
+      <c r="H44" s="4">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="I44" s="4">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="J44" s="4">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="K44" s="4">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="D4:O34">
+    <cfRule type="containsText" dxfId="11" priority="12" operator="containsText" text="Alice">
+      <formula>NOT(ISERROR(SEARCH("Alice",D4)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="10" priority="11" operator="containsText" text="Bruce">
+      <formula>NOT(ISERROR(SEARCH("Bruce",D4)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="9" priority="10" operator="containsText" text="Carol">
+      <formula>NOT(ISERROR(SEARCH("Carol",D4)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="8" priority="9" operator="containsText" text="David">
+      <formula>NOT(ISERROR(SEARCH("David",D4)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="7" priority="8" operator="containsText" text="Eason">
+      <formula>NOT(ISERROR(SEARCH("Eason",D4)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="Frank">
+      <formula>NOT(ISERROR(SEARCH("Frank",D4)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="Grog">
+      <formula>NOT(ISERROR(SEARCH("Grog",D4)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="Hank">
+      <formula>NOT(ISERROR(SEARCH("Hank",D4)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Iris">
+      <formula>NOT(ISERROR(SEARCH("Iris",D4)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Jackson">
+      <formula>NOT(ISERROR(SEARCH("Jackson",D4)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Ken">
+      <formula>NOT(ISERROR(SEARCH("Ken",D4)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Louis">
+      <formula>NOT(ISERROR(SEARCH("Louis",D4)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Lisa Project/Lisa's project.xlsx
+++ b/Lisa Project/Lisa's project.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\C語言\C-Learning\Lisa Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{388D3B8E-AE8E-4E1D-8B0C-F99F5F4D7238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E52CE182-9CDF-436B-BFE3-B5F22406C79F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{DA1E983E-EF55-4F84-98AC-5E562C614A6E}"/>
   </bookViews>
@@ -377,9 +377,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -392,11 +389,14 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="25">
+  <dxfs count="12">
     <dxf>
       <fill>
         <patternFill>
@@ -479,98 +479,6 @@
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF339966"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCCCCFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCC99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCC9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCCFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF9999FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFAE0F5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor auto="1"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -916,35 +824,35 @@
   </cols>
   <sheetData>
     <row r="5" spans="4:27" x14ac:dyDescent="0.3">
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13" t="s">
+      <c r="E5" s="17"/>
+      <c r="F5" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13" t="s">
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="13" t="s">
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="M5" s="13"/>
-      <c r="N5" s="13"/>
-      <c r="O5" s="13" t="s">
+      <c r="M5" s="17"/>
+      <c r="N5" s="17"/>
+      <c r="O5" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="P5" s="13"/>
-      <c r="Q5" s="13"/>
-      <c r="R5" s="13" t="s">
+      <c r="P5" s="17"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="S5" s="13"/>
-      <c r="T5" s="13"/>
+      <c r="S5" s="17"/>
+      <c r="T5" s="17"/>
     </row>
     <row r="6" spans="4:27" x14ac:dyDescent="0.3">
       <c r="F6" s="1" t="s">
@@ -2796,81 +2704,81 @@
       <c r="B2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14" t="s">
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14" t="s">
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14" t="s">
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="M2" s="14"/>
-      <c r="N2" s="14"/>
-      <c r="O2" s="14" t="s">
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="P2" s="14"/>
-      <c r="Q2" s="14"/>
-      <c r="R2" s="14" t="s">
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="13" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="3" spans="2:18" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15" t="s">
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="G3" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="15" t="s">
+      <c r="H3" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="I3" s="15" t="s">
+      <c r="I3" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="J3" s="15" t="s">
+      <c r="J3" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="K3" s="15" t="s">
+      <c r="K3" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="L3" s="15" t="s">
+      <c r="L3" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="M3" s="15" t="s">
+      <c r="M3" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="N3" s="15" t="s">
+      <c r="N3" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="O3" s="15" t="s">
+      <c r="O3" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="P3" s="15" t="s">
+      <c r="P3" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="Q3" s="15" t="s">
+      <c r="Q3" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="R3" s="15" t="s">
+      <c r="R3" s="14" t="s">
         <v>38</v>
       </c>
     </row>
@@ -3887,46 +3795,46 @@
       </c>
     </row>
     <row r="27" spans="2:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="17">
+      <c r="B27" s="16">
         <v>46258</v>
       </c>
-      <c r="C27" s="14" t="s">
+      <c r="C27" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="D27" s="14" t="s">
+      <c r="D27" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="E27" s="14" t="s">
+      <c r="E27" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="F27" s="14" t="s">
+      <c r="F27" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G27" s="14" t="s">
+      <c r="G27" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="H27" s="14" t="s">
+      <c r="H27" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="I27" s="14" t="s">
+      <c r="I27" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="J27" s="14" t="s">
+      <c r="J27" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="K27" s="14" t="s">
+      <c r="K27" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="L27" s="14" t="s">
+      <c r="L27" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="M27" s="14" t="s">
+      <c r="M27" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="N27" s="14" t="s">
+      <c r="N27" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="O27" s="14" t="s">
+      <c r="O27" s="13" t="s">
         <v>40</v>
       </c>
     </row>
@@ -4151,46 +4059,46 @@
       </c>
     </row>
     <row r="33" spans="2:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="17">
+      <c r="B33" s="16">
         <v>46264</v>
       </c>
-      <c r="C33" s="14" t="s">
+      <c r="C33" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D33" s="14" t="s">
+      <c r="D33" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="E33" s="14" t="s">
+      <c r="E33" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="F33" s="14" t="s">
+      <c r="F33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="G33" s="14" t="s">
+      <c r="G33" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="H33" s="14" t="s">
+      <c r="H33" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="I33" s="14" t="s">
+      <c r="I33" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="J33" s="14" t="s">
+      <c r="J33" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="K33" s="14" t="s">
+      <c r="K33" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="L33" s="14" t="s">
+      <c r="L33" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="M33" s="14" t="s">
+      <c r="M33" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="N33" s="14" t="s">
+      <c r="N33" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="O33" s="14" t="s">
+      <c r="O33" s="13" t="s">
         <v>41</v>
       </c>
     </row>
@@ -4239,19 +4147,19 @@
       </c>
     </row>
     <row r="39" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="C39" s="16">
-        <v>1</v>
-      </c>
-      <c r="D39" s="16">
-        <v>0</v>
-      </c>
-      <c r="E39" s="16">
-        <v>1</v>
-      </c>
-      <c r="F39" s="16">
-        <v>2</v>
-      </c>
-      <c r="G39" s="16">
+      <c r="C39" s="15">
+        <v>1</v>
+      </c>
+      <c r="D39" s="15">
+        <v>0</v>
+      </c>
+      <c r="E39" s="15">
+        <v>1</v>
+      </c>
+      <c r="F39" s="15">
+        <v>2</v>
+      </c>
+      <c r="G39" s="15">
         <v>3</v>
       </c>
       <c r="H39" s="4">
@@ -4272,19 +4180,19 @@
       </c>
     </row>
     <row r="40" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="C40" s="16">
-        <v>2</v>
-      </c>
-      <c r="D40" s="16">
-        <v>0</v>
-      </c>
-      <c r="E40" s="16">
-        <v>1</v>
-      </c>
-      <c r="F40" s="16">
-        <v>2</v>
-      </c>
-      <c r="G40" s="16">
+      <c r="C40" s="15">
+        <v>2</v>
+      </c>
+      <c r="D40" s="15">
+        <v>0</v>
+      </c>
+      <c r="E40" s="15">
+        <v>1</v>
+      </c>
+      <c r="F40" s="15">
+        <v>2</v>
+      </c>
+      <c r="G40" s="15">
         <v>3</v>
       </c>
       <c r="H40" s="4">
@@ -4305,19 +4213,19 @@
       </c>
     </row>
     <row r="41" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="C41" s="16">
-        <v>3</v>
-      </c>
-      <c r="D41" s="16">
-        <v>0</v>
-      </c>
-      <c r="E41" s="16">
-        <v>1</v>
-      </c>
-      <c r="F41" s="16">
-        <v>3</v>
-      </c>
-      <c r="G41" s="16">
+      <c r="C41" s="15">
+        <v>3</v>
+      </c>
+      <c r="D41" s="15">
+        <v>0</v>
+      </c>
+      <c r="E41" s="15">
+        <v>1</v>
+      </c>
+      <c r="F41" s="15">
+        <v>3</v>
+      </c>
+      <c r="G41" s="15">
         <v>2</v>
       </c>
       <c r="H41" s="4">
@@ -4338,19 +4246,19 @@
       </c>
     </row>
     <row r="42" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="C42" s="16">
+      <c r="C42" s="15">
         <v>4</v>
       </c>
-      <c r="D42" s="16">
-        <v>0</v>
-      </c>
-      <c r="E42" s="16">
-        <v>1</v>
-      </c>
-      <c r="F42" s="16">
-        <v>3</v>
-      </c>
-      <c r="G42" s="16">
+      <c r="D42" s="15">
+        <v>0</v>
+      </c>
+      <c r="E42" s="15">
+        <v>1</v>
+      </c>
+      <c r="F42" s="15">
+        <v>3</v>
+      </c>
+      <c r="G42" s="15">
         <v>2</v>
       </c>
       <c r="H42" s="4">
@@ -4371,19 +4279,19 @@
       </c>
     </row>
     <row r="43" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="C43" s="16">
+      <c r="C43" s="15">
         <v>5</v>
       </c>
-      <c r="D43" s="16">
-        <v>0</v>
-      </c>
-      <c r="E43" s="16">
-        <v>2</v>
-      </c>
-      <c r="F43" s="16">
-        <v>3</v>
-      </c>
-      <c r="G43" s="16">
+      <c r="D43" s="15">
+        <v>0</v>
+      </c>
+      <c r="E43" s="15">
+        <v>2</v>
+      </c>
+      <c r="F43" s="15">
+        <v>3</v>
+      </c>
+      <c r="G43" s="15">
         <v>1</v>
       </c>
       <c r="H43" s="4">
@@ -4404,19 +4312,19 @@
       </c>
     </row>
     <row r="44" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="C44" s="16">
+      <c r="C44" s="15">
         <v>6</v>
       </c>
-      <c r="D44" s="16">
-        <v>0</v>
-      </c>
-      <c r="E44" s="16">
-        <v>2</v>
-      </c>
-      <c r="F44" s="16">
-        <v>3</v>
-      </c>
-      <c r="G44" s="16">
+      <c r="D44" s="15">
+        <v>0</v>
+      </c>
+      <c r="E44" s="15">
+        <v>2</v>
+      </c>
+      <c r="F44" s="15">
+        <v>3</v>
+      </c>
+      <c r="G44" s="15">
         <v>1</v>
       </c>
       <c r="H44" s="4">

--- a/Lisa Project/Lisa's project.xlsx
+++ b/Lisa Project/Lisa's project.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\C語言\C-Learning\Lisa Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E52CE182-9CDF-436B-BFE3-B5F22406C79F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D06CE106-3289-4DB9-AFF1-582BDE40D200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{DA1E983E-EF55-4F84-98AC-5E562C614A6E}"/>
+    <workbookView xWindow="564" yWindow="6384" windowWidth="17280" windowHeight="8832" activeTab="1" xr2:uid="{DA1E983E-EF55-4F84-98AC-5E562C614A6E}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -2692,7 +2692,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC5B9C8A-20B7-4BD8-AC90-189B0DB1623A}">
-  <dimension ref="B2:R44"/>
+  <dimension ref="B2:R50"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="14" width="8.6640625" style="4"/>
@@ -3002,47 +3002,47 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B9" s="2">
+    <row r="9" spans="2:18" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="16">
         <v>46240</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="J9" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="K9" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="L9" s="4" t="s">
+      <c r="L9" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="M9" s="4" t="s">
+      <c r="M9" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="N9" s="4" t="s">
+      <c r="N9" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="O9" s="4" t="s">
+      <c r="O9" s="13" t="s">
         <v>41</v>
       </c>
     </row>
@@ -3266,47 +3266,47 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B15" s="2">
+    <row r="15" spans="2:18" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="16">
         <v>46246</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="H15" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="I15" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="J15" s="4" t="s">
+      <c r="J15" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="K15" s="4" t="s">
+      <c r="K15" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="L15" s="4" t="s">
+      <c r="L15" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="M15" s="4" t="s">
+      <c r="M15" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="N15" s="4" t="s">
+      <c r="N15" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="O15" s="4" t="s">
+      <c r="O15" s="13" t="s">
         <v>42</v>
       </c>
     </row>
@@ -3530,47 +3530,47 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B21" s="2">
+    <row r="21" spans="2:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="16">
         <v>46252</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="H21" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="I21" s="4" t="s">
+      <c r="I21" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="J21" s="4" t="s">
+      <c r="J21" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="K21" s="4" t="s">
+      <c r="K21" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="L21" s="4" t="s">
+      <c r="L21" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="M21" s="4" t="s">
+      <c r="M21" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="N21" s="4" t="s">
+      <c r="N21" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="O21" s="4" t="s">
+      <c r="O21" s="13" t="s">
         <v>43</v>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
         <v>1</v>
       </c>
       <c r="D39" s="15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E39" s="15">
         <v>1</v>
@@ -4168,7 +4168,7 @@
       </c>
       <c r="I39" s="4">
         <f>MOD(D39 + H39,4)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" s="4">
         <f>QUOTIENT(C39,3)+2</f>
@@ -4184,7 +4184,7 @@
         <v>2</v>
       </c>
       <c r="D40" s="15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E40" s="15">
         <v>1</v>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="I40" s="4">
         <f t="shared" ref="I40:I44" si="1">MOD(D40 + H40,4)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" s="4">
         <f t="shared" ref="J40:J44" si="2">QUOTIENT(C40,3)+2</f>
@@ -4217,7 +4217,7 @@
         <v>3</v>
       </c>
       <c r="D41" s="15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E41" s="15">
         <v>1</v>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="I41" s="4">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" s="4">
         <f t="shared" si="2"/>
@@ -4250,7 +4250,7 @@
         <v>4</v>
       </c>
       <c r="D42" s="15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E42" s="15">
         <v>1</v>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="I42" s="4">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" s="4">
         <f>QUOTIENT(C42,3)+2</f>
@@ -4283,7 +4283,7 @@
         <v>5</v>
       </c>
       <c r="D43" s="15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E43" s="15">
         <v>2</v>
@@ -4300,7 +4300,7 @@
       </c>
       <c r="I43" s="4">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J43" s="4">
         <f t="shared" si="2"/>
@@ -4316,7 +4316,7 @@
         <v>6</v>
       </c>
       <c r="D44" s="15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E44" s="15">
         <v>2</v>
@@ -4333,7 +4333,7 @@
       </c>
       <c r="I44" s="4">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J44" s="4">
         <f t="shared" si="2"/>
@@ -4342,6 +4342,38 @@
       <c r="K44" s="4">
         <f t="shared" si="3"/>
         <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="C47" s="4">
+        <v>0</v>
+      </c>
+      <c r="D47" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="C48" s="4">
+        <v>1</v>
+      </c>
+      <c r="D48" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C49" s="4">
+        <v>2</v>
+      </c>
+      <c r="D49" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C50" s="4">
+        <v>3</v>
+      </c>
+      <c r="D50" s="4">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/Lisa Project/Lisa's project.xlsx
+++ b/Lisa Project/Lisa's project.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\C語言\C-Learning\Lisa Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D06CE106-3289-4DB9-AFF1-582BDE40D200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C88BEE64-ABD6-454C-8DE8-6C96E58857CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="564" yWindow="6384" windowWidth="17280" windowHeight="8832" activeTab="1" xr2:uid="{DA1E983E-EF55-4F84-98AC-5E562C614A6E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{DA1E983E-EF55-4F84-98AC-5E562C614A6E}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -2692,7 +2692,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC5B9C8A-20B7-4BD8-AC90-189B0DB1623A}">
-  <dimension ref="B2:R50"/>
+  <dimension ref="B2:R55"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="14" width="8.6640625" style="4"/>
@@ -4360,7 +4360,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C49" s="4">
         <v>2</v>
       </c>
@@ -4368,12 +4368,38 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C50" s="4">
         <v>3</v>
       </c>
       <c r="D50" s="4">
         <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C52" s="4">
+        <v>0</v>
+      </c>
+      <c r="D52" s="4">
+        <v>0</v>
+      </c>
+      <c r="E52" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C53" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C54" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="3:5" x14ac:dyDescent="0.3">
+      <c r="C55" s="4">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
